--- a/domain/tasks/20260310_115400_vd_ingame_masterdata_generation/vd-ingame-creator/vd_aya_normal_00001/vd_aya_normal_00001.xlsx
+++ b/domain/tasks/20260310_115400_vd_ingame_masterdata_generation/vd-ingame-creator/vd_aya_normal_00001/vd_aya_normal_00001.xlsx
@@ -980,7 +980,11 @@
           <t>2コマ</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr"/>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>aya_00002</t>
+        </is>
+      </c>
       <c r="E14" s="26" t="inlineStr">
         <is>
           <t>None</t>
@@ -1011,7 +1015,11 @@
           <t>3コマ</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr"/>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>aya_00002</t>
+        </is>
+      </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
           <t>None</t>
@@ -1042,7 +1050,11 @@
           <t>3コマ</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr"/>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>aya_00002</t>
+        </is>
+      </c>
       <c r="E16" s="26" t="inlineStr">
         <is>
           <t>None</t>
@@ -1277,7 +1289,7 @@
       </c>
       <c r="I26" s="26" t="inlineStr">
         <is>
-          <t>雑魚</t>
+          <t>雑魚（e_キャラ）</t>
         </is>
       </c>
       <c r="J26" s="2" t="n"/>
@@ -1564,7 +1576,11 @@
       <c r="G40" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H40" s="26" t="inlineStr"/>
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>開幕5体・序盤の圧力</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
@@ -1597,7 +1613,11 @@
       <c r="G41" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H41" s="26" t="inlineStr"/>
+      <c r="H41" s="26" t="inlineStr">
+        <is>
+          <t>第2波5体</t>
+        </is>
+      </c>
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
@@ -1630,7 +1650,11 @@
       <c r="G42" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H42" s="26" t="inlineStr"/>
+      <c r="H42" s="26" t="inlineStr">
+        <is>
+          <t>第3波5体・合計15体</t>
+        </is>
+      </c>
       <c r="I42" s="2" t="n"/>
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
@@ -1881,7 +1905,7 @@
           <t>バトルヒント</t>
         </is>
       </c>
-      <c r="C58" s="26" t="inlineStr"/>
+      <c r="C58" s="18" t="inlineStr"/>
       <c r="D58" s="27" t="n"/>
       <c r="E58" s="27" t="n"/>
       <c r="F58" s="27" t="n"/>
@@ -1900,7 +1924,7 @@
           <t>ステージ説明文</t>
         </is>
       </c>
-      <c r="C59" s="26" t="inlineStr"/>
+      <c r="C59" s="18" t="inlineStr"/>
       <c r="D59" s="27" t="n"/>
       <c r="E59" s="27" t="n"/>
       <c r="F59" s="27" t="n"/>
@@ -2293,7 +2317,11 @@
         </is>
       </c>
       <c r="AD2" s="31" t="inlineStr"/>
-      <c r="AE2" s="31" t="inlineStr"/>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AF2" s="31" t="inlineStr"/>
       <c r="AG2" s="31" t="inlineStr">
         <is>
@@ -2410,7 +2438,11 @@
         </is>
       </c>
       <c r="AD3" s="31" t="inlineStr"/>
-      <c r="AE3" s="31" t="inlineStr"/>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AF3" s="31" t="inlineStr"/>
       <c r="AG3" s="31" t="inlineStr">
         <is>
@@ -2527,7 +2559,11 @@
         </is>
       </c>
       <c r="AD4" s="31" t="inlineStr"/>
-      <c r="AE4" s="31" t="inlineStr"/>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AF4" s="31" t="inlineStr"/>
       <c r="AG4" s="31" t="inlineStr">
         <is>
@@ -3269,13 +3305,21 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G2" s="31" t="inlineStr"/>
+      <c r="G2" s="31" t="inlineStr">
+        <is>
+          <t>aya_00002</t>
+        </is>
+      </c>
       <c r="H2" s="31" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="I2" s="31" t="inlineStr"/>
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
       <c r="J2" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -3446,13 +3490,21 @@
           <t>9</t>
         </is>
       </c>
-      <c r="G3" s="31" t="inlineStr"/>
+      <c r="G3" s="31" t="inlineStr">
+        <is>
+          <t>aya_00002</t>
+        </is>
+      </c>
       <c r="H3" s="31" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="I3" s="31" t="inlineStr"/>
+      <c r="I3" s="31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
       <c r="J3" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -3627,13 +3679,21 @@
           <t>7</t>
         </is>
       </c>
-      <c r="G4" s="31" t="inlineStr"/>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>aya_00002</t>
+        </is>
+      </c>
       <c r="H4" s="31" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr"/>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
       <c r="J4" s="31" t="inlineStr">
         <is>
           <t>None</t>
